--- a/04_Figures/F04_association/modules/trajectory/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/trajectory/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -72,12 +72,6 @@
     <t xml:space="preserve">ME_red@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T1</t>
   </si>
   <si>
@@ -111,12 +105,6 @@
     <t xml:space="preserve">ME_red@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T2</t>
   </si>
   <si>
@@ -148,12 +136,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise@T3</t>
@@ -570,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00123952596307669</v>
+        <v>-0.00216657063352135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.267196344952196</v>
+        <v>-0.468545492670235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.789435693368814</v>
+        <v>0.639907478236275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="3">
@@ -593,16 +575,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00158989686323927</v>
+        <v>0.00250652020748072</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.343506659700699</v>
+        <v>0.558006748119149</v>
       </c>
       <c r="F3" t="n">
-        <v>0.731371593807931</v>
+        <v>0.577467124354631</v>
       </c>
       <c r="G3" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="4">
@@ -616,16 +598,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00386988194250164</v>
+        <v>0.000489006101813971</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.837290017354727</v>
+        <v>0.105645133423214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.40285692880774</v>
+        <v>0.91597034885317</v>
       </c>
       <c r="G4" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="5">
@@ -639,16 +621,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00194045560462792</v>
+        <v>0.00139763412377434</v>
       </c>
       <c r="E5" t="n">
-        <v>0.421280982411572</v>
+        <v>0.297329744163493</v>
       </c>
       <c r="F5" t="n">
-        <v>0.673743328375849</v>
+        <v>0.76652498363735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="6">
@@ -662,16 +644,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00523527188812974</v>
+        <v>-0.0058100234851625</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.12904015953205</v>
+        <v>-1.25229334750534</v>
       </c>
       <c r="F6" t="n">
-        <v>0.25945928469076</v>
+        <v>0.211933046282068</v>
       </c>
       <c r="G6" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="7">
@@ -685,16 +667,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00717216257388268</v>
+        <v>0.00100991206318359</v>
       </c>
       <c r="E7" t="n">
-        <v>1.54695604325643</v>
+        <v>0.216969958982952</v>
       </c>
       <c r="F7" t="n">
-        <v>0.122549767958408</v>
+        <v>0.828454080589811</v>
       </c>
       <c r="G7" t="n">
-        <v>0.79657349172965</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="8">
@@ -708,16 +690,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000433372250987627</v>
+        <v>0.00120532866080154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.093506969940862</v>
+        <v>0.263658054018024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.925540829634274</v>
+        <v>0.792316292155667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="9">
@@ -731,16 +713,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.000412698312504209</v>
+        <v>0.0015083384708524</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0891762566443867</v>
+        <v>0.321203490959422</v>
       </c>
       <c r="F9" t="n">
-        <v>0.928979983333886</v>
+        <v>0.748393348075499</v>
       </c>
       <c r="G9" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +736,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00143849987817995</v>
+        <v>0.00267131792369169</v>
       </c>
       <c r="E10" t="n">
-        <v>0.309454816910046</v>
+        <v>0.561257033858766</v>
       </c>
       <c r="F10" t="n">
-        <v>0.757113307175841</v>
+        <v>0.575253928685134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="11">
@@ -777,16 +759,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00268219973473846</v>
+        <v>-0.00116146891304973</v>
       </c>
       <c r="E11" t="n">
-        <v>0.58105069219657</v>
+        <v>-0.25074366995488</v>
       </c>
       <c r="F11" t="n">
-        <v>0.561486001834971</v>
+        <v>0.802271048631709</v>
       </c>
       <c r="G11" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="12">
@@ -800,16 +782,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00420287092248404</v>
+        <v>-0.00375855913704049</v>
       </c>
       <c r="E12" t="n">
-        <v>0.910137256889355</v>
+        <v>-0.822381519282117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.363218628531642</v>
+        <v>0.411844288746652</v>
       </c>
       <c r="G12" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="13">
@@ -823,16 +805,16 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00139074589276789</v>
+        <v>0.00024476309661099</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.300082377448717</v>
+        <v>0.0541045213289714</v>
       </c>
       <c r="F13" t="n">
-        <v>0.76424756323976</v>
+        <v>0.956906178465525</v>
       </c>
       <c r="G13" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="14">
@@ -846,16 +828,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00247246904545623</v>
+        <v>0.00118466278393744</v>
       </c>
       <c r="E14" t="n">
-        <v>0.531896430231288</v>
+        <v>0.257883478988773</v>
       </c>
       <c r="F14" t="n">
-        <v>0.595050122476921</v>
+        <v>0.796763381186474</v>
       </c>
       <c r="G14" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="15">
@@ -869,16 +851,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000709180025530301</v>
+        <v>0.00463732159052897</v>
       </c>
       <c r="E15" t="n">
-        <v>0.153041910647555</v>
+        <v>1.01724509450108</v>
       </c>
       <c r="F15" t="n">
-        <v>0.878431186841266</v>
+        <v>0.310272244232817</v>
       </c>
       <c r="G15" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="16">
@@ -892,16 +874,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00290078450386257</v>
+        <v>-0.00157661119080007</v>
       </c>
       <c r="E16" t="n">
-        <v>0.628340272711153</v>
+        <v>-0.345098711783908</v>
       </c>
       <c r="F16" t="n">
-        <v>0.530087567884783</v>
+        <v>0.730384716390017</v>
       </c>
       <c r="G16" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="17">
@@ -915,16 +897,16 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.000782027192568186</v>
+        <v>0.000244008956267654</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.169434558404341</v>
+        <v>0.0530988967575676</v>
       </c>
       <c r="F17" t="n">
-        <v>0.865528053681555</v>
+        <v>0.957706387017635</v>
       </c>
       <c r="G17" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="18">
@@ -938,16 +920,16 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0013726157449454</v>
+        <v>0.000492126506001697</v>
       </c>
       <c r="E18" t="n">
-        <v>0.297193000709603</v>
+        <v>0.106383236413513</v>
       </c>
       <c r="F18" t="n">
-        <v>0.766451029515475</v>
+        <v>0.915385479863404</v>
       </c>
       <c r="G18" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="19">
@@ -961,16 +943,16 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000287270741243129</v>
+        <v>0.00173947490873</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0620797486556406</v>
+        <v>0.384449135885561</v>
       </c>
       <c r="F19" t="n">
-        <v>0.950525827494325</v>
+        <v>0.701056186231172</v>
       </c>
       <c r="G19" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="20">
@@ -984,16 +966,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00150184008335906</v>
+        <v>0.00471095957660025</v>
       </c>
       <c r="E20" t="n">
-        <v>0.324572027490407</v>
+        <v>1.04031648504415</v>
       </c>
       <c r="F20" t="n">
-        <v>0.745650025444764</v>
+        <v>0.299455429404325</v>
       </c>
       <c r="G20" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="21">
@@ -1007,16 +989,16 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00474965125752895</v>
+        <v>0.00315052321330756</v>
       </c>
       <c r="E21" t="n">
-        <v>1.02802275765028</v>
+        <v>0.694158998342002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.304470143311722</v>
+        <v>0.488392221082264</v>
       </c>
       <c r="G21" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="22">
@@ -1030,16 +1012,16 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.000137689101544615</v>
+        <v>-0.00381302180787042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0298123929864523</v>
+        <v>-0.830277940440223</v>
       </c>
       <c r="F22" t="n">
-        <v>0.976229383872881</v>
+        <v>0.407376819812681</v>
       </c>
       <c r="G22" t="n">
-        <v>0.976229383872881</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="23">
@@ -1053,16 +1035,16 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0010446835273072</v>
+        <v>-0.00179358354488069</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.226084750429761</v>
+        <v>-0.394610295570415</v>
       </c>
       <c r="F23" t="n">
-        <v>0.82123420908354</v>
+        <v>0.693553192676209</v>
       </c>
       <c r="G23" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="24">
@@ -1076,16 +1058,16 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00121615539133956</v>
+        <v>-0.00800020386203292</v>
       </c>
       <c r="E24" t="n">
-        <v>0.261207032561525</v>
+        <v>-1.72906274164676</v>
       </c>
       <c r="F24" t="n">
-        <v>0.79404776183029</v>
+        <v>0.0853490063620143</v>
       </c>
       <c r="G24" t="n">
-        <v>0.975539665059966</v>
+        <v>0.563303441989294</v>
       </c>
     </row>
     <row r="25">
@@ -1099,16 +1081,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.00305625614672247</v>
+        <v>0.00225963595743908</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.660128429121675</v>
+        <v>0.487231172854642</v>
       </c>
       <c r="F25" t="n">
-        <v>0.509496168757594</v>
+        <v>0.626630897774647</v>
       </c>
       <c r="G25" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="26">
@@ -1122,16 +1104,16 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.00385059946240325</v>
+        <v>-0.0105221230025942</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.832177706451013</v>
+        <v>-2.29546995410255</v>
       </c>
       <c r="F26" t="n">
-        <v>0.40573307301249</v>
+        <v>0.0227487156747003</v>
       </c>
       <c r="G26" t="n">
-        <v>0.975539665059966</v>
+        <v>0.250235872421703</v>
       </c>
     </row>
     <row r="27">
@@ -1145,16 +1127,16 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00352939230974547</v>
+        <v>0.00799999427645183</v>
       </c>
       <c r="E27" t="n">
-        <v>0.764091269461405</v>
+        <v>1.75486862522254</v>
       </c>
       <c r="F27" t="n">
-        <v>0.445197909770006</v>
+        <v>0.0808210361964807</v>
       </c>
       <c r="G27" t="n">
-        <v>0.975539665059966</v>
+        <v>0.563303441989294</v>
       </c>
     </row>
     <row r="28">
@@ -1168,16 +1150,16 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000449207137872465</v>
+        <v>-0.00498045157373336</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0973631793926813</v>
+        <v>-1.08109865881449</v>
       </c>
       <c r="F28" t="n">
-        <v>0.922479666584871</v>
+        <v>0.280961890543912</v>
       </c>
       <c r="G28" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="29">
@@ -1191,16 +1173,16 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0110963781208048</v>
+        <v>0.000399137655086981</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.39592515615975</v>
+        <v>0.0881710024084341</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0169702262942156</v>
+        <v>0.929829447173503</v>
       </c>
       <c r="G29" t="n">
-        <v>0.165459706368602</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="30">
@@ -1214,16 +1196,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.012121564240699</v>
+        <v>0.0133621071771448</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.6258498529217</v>
+        <v>2.90331788248134</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00892642801384009</v>
+        <v>0.00410916594943138</v>
       </c>
       <c r="G30" t="n">
-        <v>0.165459706368602</v>
+        <v>0.131839123434602</v>
       </c>
     </row>
     <row r="31">
@@ -1237,16 +1219,16 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00119262623388939</v>
+        <v>-0.00100307247800281</v>
       </c>
       <c r="E31" t="n">
-        <v>0.256962915944064</v>
+        <v>-0.218355490633707</v>
       </c>
       <c r="F31" t="n">
-        <v>0.797320331939125</v>
+        <v>0.827375947192332</v>
       </c>
       <c r="G31" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="32">
@@ -1260,16 +1242,16 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00452071235447423</v>
+        <v>-0.00336648858285814</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.976408251719889</v>
+        <v>-0.740070510502384</v>
       </c>
       <c r="F32" t="n">
-        <v>0.329366623066976</v>
+        <v>0.460129601688081</v>
       </c>
       <c r="G32" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="33">
@@ -1283,16 +1265,16 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.000524962826718085</v>
+        <v>0.00389907174913553</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.113441422739076</v>
+        <v>0.845145620374299</v>
       </c>
       <c r="F33" t="n">
-        <v>0.909729247074146</v>
+        <v>0.399044719766664</v>
       </c>
       <c r="G33" t="n">
-        <v>0.975539665059966</v>
+        <v>0.957706387017635</v>
       </c>
     </row>
     <row r="34">
@@ -1306,154 +1288,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00428363591625512</v>
+        <v>-0.012162812820156</v>
       </c>
       <c r="E34" t="n">
-        <v>0.924888762150746</v>
+        <v>-2.67951916289712</v>
       </c>
       <c r="F34" t="n">
-        <v>0.355500417088717</v>
+        <v>0.0079902499051274</v>
       </c>
       <c r="G34" t="n">
-        <v>0.975539665059966</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0119279923493023</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.57881996987311</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0102181631866028</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.165459706368602</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.00864410373466183</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.8707831612093</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0619989712118319</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.483591975452289</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.000598171421487756</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.129705775026213</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.896854940694462</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.975539665059966</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0111909978377825</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.41524597938477</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.0161068390472118</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.165459706368602</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.00359136355893431</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.775560754136247</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.43840009705092</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.975539665059966</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.00403827406960666</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.87377927662282</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.382686603710752</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.975539665059966</v>
+        <v>0.131839123434602</v>
       </c>
     </row>
   </sheetData>
@@ -1492,7 +1336,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1501,21 +1345,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000215579778367726</v>
+        <v>0.00000319788368714682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.782836624321473</v>
+        <v>0.11580885516205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.434433280746873</v>
+        <v>0.907988617049609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1524,21 +1368,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00000922478269644206</v>
+        <v>0.00000750995947165974</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.337540318073321</v>
+        <v>0.284461597231278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.735981124288384</v>
+        <v>0.776524182345446</v>
       </c>
       <c r="G3" t="n">
-        <v>0.90208972232292</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1547,21 +1391,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000329531215005662</v>
+        <v>-0.00000620097812025527</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.21410766748882</v>
+        <v>-0.224425595414215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.225804822442137</v>
+        <v>0.822790108785172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1570,21 +1414,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00000378091564387161</v>
+        <v>-0.0000147045235671004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14091949651044</v>
+        <v>-0.520208169550947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.888042317813237</v>
+        <v>0.603832395861812</v>
       </c>
       <c r="G5" t="n">
-        <v>0.928564282978879</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1593,21 +1437,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00000356420283090901</v>
+        <v>-0.00000727310394173056</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.129207981874312</v>
+        <v>-0.260766438401743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.897292666312859</v>
+        <v>0.79469883266373</v>
       </c>
       <c r="G6" t="n">
-        <v>0.928564282978879</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1616,21 +1460,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000459429521754048</v>
+        <v>0.0000211273630876948</v>
       </c>
       <c r="E7" t="n">
-        <v>1.67170144458216</v>
+        <v>0.759660909724031</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0957825012983647</v>
+        <v>0.448877937377618</v>
       </c>
       <c r="G7" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1639,21 +1483,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000218431384634818</v>
+        <v>0.0000282031491703857</v>
       </c>
       <c r="E8" t="n">
-        <v>0.79613778838352</v>
+        <v>1.0444873046106</v>
       </c>
       <c r="F8" t="n">
-        <v>0.426675997274722</v>
+        <v>0.298262071816423</v>
       </c>
       <c r="G8" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1662,21 +1506,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000230474607372297</v>
+        <v>0.0000204449994082923</v>
       </c>
       <c r="E9" t="n">
-        <v>0.844838914246123</v>
+        <v>0.725077619889229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.398975103619494</v>
+        <v>0.469750420143618</v>
       </c>
       <c r="G9" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1685,21 +1529,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000154801711921781</v>
+        <v>-0.00000176619871790409</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.557497266606754</v>
+        <v>-0.0612151225233684</v>
       </c>
       <c r="F10" t="n">
-        <v>0.577665884176734</v>
+        <v>0.95128499375421</v>
       </c>
       <c r="G10" t="n">
-        <v>0.901158779315705</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1708,21 +1552,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000260259614977856</v>
+        <v>-0.00000817874447019192</v>
       </c>
       <c r="E11" t="n">
-        <v>0.963201155964198</v>
+        <v>-0.29566430451078</v>
       </c>
       <c r="F11" t="n">
-        <v>0.336338775599141</v>
+        <v>0.767973727279508</v>
       </c>
       <c r="G11" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1731,21 +1575,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000128058052127997</v>
+        <v>-0.0000313009762463686</v>
       </c>
       <c r="E12" t="n">
-        <v>0.472168173723561</v>
+        <v>-1.15810689426124</v>
       </c>
       <c r="F12" t="n">
-        <v>0.637201569497104</v>
+        <v>0.249013436303442</v>
       </c>
       <c r="G12" t="n">
-        <v>0.90208972232292</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -1754,21 +1598,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00000916083999106826</v>
+        <v>0.0000175209118811947</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.333537649295283</v>
+        <v>0.6580136384041</v>
       </c>
       <c r="F13" t="n">
-        <v>0.738996468500136</v>
+        <v>0.511731206051418</v>
       </c>
       <c r="G13" t="n">
-        <v>0.90208972232292</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1777,21 +1621,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00000493709493196946</v>
+        <v>-0.0000262886898803228</v>
       </c>
       <c r="E14" t="n">
-        <v>0.177659607138666</v>
+        <v>-0.965730764689915</v>
       </c>
       <c r="F14" t="n">
-        <v>0.859128211477166</v>
+        <v>0.336031013885682</v>
       </c>
       <c r="G14" t="n">
-        <v>0.928564282978879</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -1800,21 +1644,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0000324118887578356</v>
+        <v>0.0000294856917266678</v>
       </c>
       <c r="E15" t="n">
-        <v>1.18378053798905</v>
+        <v>1.09310337717951</v>
       </c>
       <c r="F15" t="n">
-        <v>0.237577737658441</v>
+        <v>0.276436354665616</v>
       </c>
       <c r="G15" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -1823,21 +1667,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0000243651004802885</v>
+        <v>-0.00000808594329999319</v>
       </c>
       <c r="E16" t="n">
-        <v>0.901086243188986</v>
+        <v>-0.298517936410548</v>
       </c>
       <c r="F16" t="n">
-        <v>0.368373786523184</v>
+        <v>0.76580020767463</v>
       </c>
       <c r="G16" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -1846,21 +1690,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000092762828361924</v>
+        <v>0.0000276327720641681</v>
       </c>
       <c r="E17" t="n">
-        <v>0.343155385124754</v>
+        <v>1.01521240710019</v>
       </c>
       <c r="F17" t="n">
-        <v>0.731758000982812</v>
+        <v>0.311952350629285</v>
       </c>
       <c r="G17" t="n">
-        <v>0.90208972232292</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -1869,21 +1713,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0000213344143904806</v>
+        <v>0.0000310427431164559</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.787846166295419</v>
+        <v>1.12999459358324</v>
       </c>
       <c r="F18" t="n">
-        <v>0.431502125293616</v>
+        <v>0.260627544312421</v>
       </c>
       <c r="G18" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -1892,21 +1736,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0000278187985054645</v>
+        <v>0.0000252405538950266</v>
       </c>
       <c r="E19" t="n">
-        <v>1.02076420002626</v>
+        <v>0.948914566129102</v>
       </c>
       <c r="F19" t="n">
-        <v>0.308312070831682</v>
+        <v>0.344482676794783</v>
       </c>
       <c r="G19" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -1915,21 +1759,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0000214959901741154</v>
+        <v>0.0000242325213472123</v>
       </c>
       <c r="E20" t="n">
-        <v>0.788173792037702</v>
+        <v>0.906217606618803</v>
       </c>
       <c r="F20" t="n">
-        <v>0.431310829256668</v>
+        <v>0.366552433751914</v>
       </c>
       <c r="G20" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -1938,21 +1782,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0000387632050665907</v>
+        <v>0.00000184298062744743</v>
       </c>
       <c r="E21" t="n">
-        <v>1.43082220215974</v>
+        <v>0.0686183689056932</v>
       </c>
       <c r="F21" t="n">
-        <v>0.153678219108386</v>
+        <v>0.945402300340766</v>
       </c>
       <c r="G21" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -1961,21 +1805,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0000238993680412578</v>
+        <v>-0.0000317274342299727</v>
       </c>
       <c r="E22" t="n">
-        <v>0.883042512236438</v>
+        <v>-1.16519284048238</v>
       </c>
       <c r="F22" t="n">
-        <v>0.378026497642086</v>
+        <v>0.246144675505632</v>
       </c>
       <c r="G22" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -1984,21 +1828,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.00000901403394250857</v>
+        <v>0.00000285770161251932</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.33197311921769</v>
+        <v>0.106296957996128</v>
       </c>
       <c r="F23" t="n">
-        <v>0.740176182418806</v>
+        <v>0.915515994773791</v>
       </c>
       <c r="G23" t="n">
-        <v>0.90208972232292</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2007,21 +1851,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0000298538623382119</v>
+        <v>-0.00000827427496084372</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.07057491735155</v>
+        <v>-0.296320412678782</v>
       </c>
       <c r="F24" t="n">
-        <v>0.285350331296524</v>
+        <v>0.767473826615825</v>
       </c>
       <c r="G24" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2030,21 +1874,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0000425827933366182</v>
+        <v>-0.0000248831272185436</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.56237327001385</v>
+        <v>-0.899843602987915</v>
       </c>
       <c r="F25" t="n">
-        <v>0.119412622404262</v>
+        <v>0.369922065699773</v>
       </c>
       <c r="G25" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2053,21 +1897,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0000313526799561051</v>
+        <v>-0.0000248954056194892</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.14984396254373</v>
+        <v>-0.89919357291993</v>
       </c>
       <c r="F26" t="n">
-        <v>0.251261406691866</v>
+        <v>0.370266796776998</v>
       </c>
       <c r="G26" t="n">
-        <v>0.770131724960366</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -2076,21 +1920,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.000000768599081607338</v>
+        <v>0.0000161139289565804</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0283114584967212</v>
+        <v>0.59072343269563</v>
       </c>
       <c r="F27" t="n">
-        <v>0.977435392860665</v>
+        <v>0.555765097328235</v>
       </c>
       <c r="G27" t="n">
-        <v>0.977435392860665</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -2099,21 +1943,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0000119973311059027</v>
+        <v>0.0000059860783428547</v>
       </c>
       <c r="E28" t="n">
-        <v>0.444565947283035</v>
+        <v>0.217257596122758</v>
       </c>
       <c r="F28" t="n">
-        <v>0.657002143888845</v>
+        <v>0.828359424682159</v>
       </c>
       <c r="G28" t="n">
-        <v>0.90208972232292</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -2122,21 +1966,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.000022761374547208</v>
+        <v>0.0000118505114974798</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.823064697046352</v>
+        <v>0.444176747185132</v>
       </c>
       <c r="F29" t="n">
-        <v>0.411223123227084</v>
+        <v>0.657677622553802</v>
       </c>
       <c r="G29" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -2145,21 +1989,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.000042357475806397</v>
+        <v>0.0000618083407744014</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.5524624787688</v>
+        <v>2.22898393269111</v>
       </c>
       <c r="F30" t="n">
-        <v>0.121764187420858</v>
+        <v>0.0275893298754544</v>
       </c>
       <c r="G30" t="n">
-        <v>0.770131724960366</v>
+        <v>0.910447885889994</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -2168,21 +2012,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0000324064622117955</v>
+        <v>0.0000123165110858323</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.17639415025271</v>
+        <v>0.451189333006202</v>
       </c>
       <c r="F31" t="n">
-        <v>0.240510006482118</v>
+        <v>0.652629577187659</v>
       </c>
       <c r="G31" t="n">
-        <v>0.770131724960366</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -2191,21 +2035,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00000798494050809003</v>
+        <v>-0.0000169781436644301</v>
       </c>
       <c r="E32" t="n">
-        <v>0.291334901637226</v>
+        <v>-0.630738937029223</v>
       </c>
       <c r="F32" t="n">
-        <v>0.771026762027418</v>
+        <v>0.529354970623271</v>
       </c>
       <c r="G32" t="n">
-        <v>0.911213446032403</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -2214,21 +2058,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0000100154890801192</v>
+        <v>0.00000419115153497067</v>
       </c>
       <c r="E33" t="n">
-        <v>0.366808161846983</v>
+        <v>0.152027272393137</v>
       </c>
       <c r="F33" t="n">
-        <v>0.714059536624073</v>
+        <v>0.879408871824659</v>
       </c>
       <c r="G33" t="n">
-        <v>0.90208972232292</v>
+        <v>0.95128499375421</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -2237,154 +2081,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0000332721541309377</v>
+        <v>-0.0000418074291621261</v>
       </c>
       <c r="E34" t="n">
-        <v>1.21584424756547</v>
+        <v>-1.53113142329906</v>
       </c>
       <c r="F34" t="n">
-        <v>0.225143594399976</v>
+        <v>0.128246734864602</v>
       </c>
       <c r="G34" t="n">
-        <v>0.770131724960366</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0000601413550269105</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.19892862862436</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.028761209442103</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.770131724960366</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0000181080516377558</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.663055753340672</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.507880429053357</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.825305697211705</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.00000478423840403883</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.177517893844423</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.859239400056869</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.928564282978879</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0000227654483737243</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.821655045257799</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.412023716478104</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.770131724960366</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.00000328298462500957</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.119773299864134</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.904754942389677</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.928564282978879</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.0000194509150674662</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.715414165693371</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.474993117416433</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.805423112140907</v>
+        <v>0.939908022587765</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2129,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2432,21 +2138,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000192801918641523</v>
+        <v>0.00000443438487346523</v>
       </c>
       <c r="E2" t="n">
-        <v>0.64998567609848</v>
+        <v>0.149386224211531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.516464999209979</v>
+        <v>0.881548608499881</v>
       </c>
       <c r="G2" t="n">
-        <v>0.808305686490898</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2455,21 +2161,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00000879147637632111</v>
+        <v>0.0000131790671895179</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.299532988052656</v>
+        <v>0.470297053978297</v>
       </c>
       <c r="F3" t="n">
-        <v>0.764851819902615</v>
+        <v>0.639163031389548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.852263456462914</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2478,21 +2184,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000424069480402937</v>
+        <v>-0.00000542257179816891</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.46073532835724</v>
+        <v>-0.182512266031796</v>
       </c>
       <c r="F4" t="n">
-        <v>0.14569438825533</v>
+        <v>0.855548825523293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2501,21 +2207,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00000990293557252113</v>
+        <v>-0.0000266608385197132</v>
       </c>
       <c r="E5" t="n">
-        <v>0.345981870416904</v>
+        <v>-0.874490579174129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.729728620171776</v>
+        <v>0.38393864131626</v>
       </c>
       <c r="G5" t="n">
-        <v>0.852263456462914</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2524,21 +2230,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0000182759016689113</v>
+        <v>-0.0000214245831758299</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.615606902721016</v>
+        <v>-0.71431885923832</v>
       </c>
       <c r="F6" t="n">
-        <v>0.538870457660599</v>
+        <v>0.476687850740174</v>
       </c>
       <c r="G6" t="n">
-        <v>0.808305686490898</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2547,21 +2253,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000517608316079852</v>
+        <v>0.0000189432869410047</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7517667474046</v>
+        <v>0.631906771538458</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0813829707304164</v>
+        <v>0.528884352021917</v>
       </c>
       <c r="G7" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2570,21 +2276,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000259237748443901</v>
+        <v>0.0000269906840888051</v>
       </c>
       <c r="E8" t="n">
-        <v>0.879018448213009</v>
+        <v>0.934190261295786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.380471093908563</v>
+        <v>0.352447565684003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2593,21 +2299,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000203641539666024</v>
+        <v>0.0000309159529414471</v>
       </c>
       <c r="E9" t="n">
-        <v>0.69512654867543</v>
+        <v>1.01724628688602</v>
       </c>
       <c r="F9" t="n">
-        <v>0.487801907227683</v>
+        <v>0.31148184947325</v>
       </c>
       <c r="G9" t="n">
-        <v>0.808305686490898</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2616,21 +2322,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000273861440983984</v>
+        <v>0.00000591262521292231</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.914845619060647</v>
+        <v>0.188660509836244</v>
       </c>
       <c r="F10" t="n">
-        <v>0.361400389235783</v>
+        <v>0.850739805282093</v>
       </c>
       <c r="G10" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2639,21 +2345,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000280833275863225</v>
+        <v>-0.00000581783700589512</v>
       </c>
       <c r="E11" t="n">
-        <v>0.971622741014014</v>
+        <v>-0.195502819106428</v>
       </c>
       <c r="F11" t="n">
-        <v>0.332439632982852</v>
+        <v>0.845394527525013</v>
       </c>
       <c r="G11" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2662,21 +2368,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000151735476755096</v>
+        <v>-0.0000413444307387938</v>
       </c>
       <c r="E12" t="n">
-        <v>0.522397609058771</v>
+        <v>-1.4358482254541</v>
       </c>
       <c r="F12" t="n">
-        <v>0.601985351462228</v>
+        <v>0.154154532807365</v>
       </c>
       <c r="G12" t="n">
-        <v>0.838479596679532</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -2685,21 +2391,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00000690127629717277</v>
+        <v>0.0000191560966146467</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.233557517476856</v>
+        <v>0.675743610754885</v>
       </c>
       <c r="F13" t="n">
-        <v>0.815573045552486</v>
+        <v>0.500757272219888</v>
       </c>
       <c r="G13" t="n">
-        <v>0.883537466015193</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -2708,21 +2414,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000164221366454711</v>
+        <v>-0.0000313247468302887</v>
       </c>
       <c r="E14" t="n">
-        <v>0.547641263480133</v>
+        <v>-1.07551977245479</v>
       </c>
       <c r="F14" t="n">
-        <v>0.584563334089074</v>
+        <v>0.284720388354806</v>
       </c>
       <c r="G14" t="n">
-        <v>0.838479596679532</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -2731,21 +2437,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0000188667852154854</v>
+        <v>0.000029496570858368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6396427274906</v>
+        <v>1.02258852364453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.523154215589912</v>
+        <v>0.308960564734455</v>
       </c>
       <c r="G15" t="n">
-        <v>0.808305686490898</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -2754,21 +2460,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0000249639876454292</v>
+        <v>-0.000010005296812101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.862683229786391</v>
+        <v>-0.345364945197001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.389369358286995</v>
+        <v>0.730542708606204</v>
       </c>
       <c r="G16" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -2777,21 +2483,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000100590144862182</v>
+        <v>0.0000235419763058746</v>
       </c>
       <c r="E17" t="n">
-        <v>0.347806686778749</v>
+        <v>0.805994786919774</v>
       </c>
       <c r="F17" t="n">
-        <v>0.728359797342762</v>
+        <v>0.4221511656361</v>
       </c>
       <c r="G17" t="n">
-        <v>0.852263456462914</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -2800,21 +2506,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0000260177938892378</v>
+        <v>0.0000180256987761745</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8979101735769</v>
+        <v>0.608423286450375</v>
       </c>
       <c r="F18" t="n">
-        <v>0.370338627681564</v>
+        <v>0.544281073879252</v>
       </c>
       <c r="G18" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -2823,21 +2529,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0000230702221636144</v>
+        <v>0.0000302382360863674</v>
       </c>
       <c r="E19" t="n">
-        <v>0.788172789678365</v>
+        <v>1.06919124263105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.431550895545949</v>
+        <v>0.287547869641796</v>
       </c>
       <c r="G19" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -2846,21 +2552,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0000233747289172214</v>
+        <v>0.0000272469632223906</v>
       </c>
       <c r="E20" t="n">
-        <v>0.798675520179859</v>
+        <v>0.956263860344796</v>
       </c>
       <c r="F20" t="n">
-        <v>0.425448391167725</v>
+        <v>0.341236321071733</v>
       </c>
       <c r="G20" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -2869,21 +2575,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0000440829810754819</v>
+        <v>0.00000423802854813815</v>
       </c>
       <c r="E21" t="n">
-        <v>1.52070940989009</v>
+        <v>0.147860792786212</v>
       </c>
       <c r="F21" t="n">
-        <v>0.12994951446532</v>
+        <v>0.882749233263237</v>
       </c>
       <c r="G21" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -2892,21 +2598,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.000028519717389672</v>
+        <v>-0.0000275812920275592</v>
       </c>
       <c r="E22" t="n">
-        <v>0.98497839168148</v>
+        <v>-0.943415014385055</v>
       </c>
       <c r="F22" t="n">
-        <v>0.325852901146479</v>
+        <v>0.347733807697763</v>
       </c>
       <c r="G22" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -2915,21 +2621,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0000113535692884922</v>
+        <v>0.00000212700048930763</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.390264343225968</v>
+        <v>0.074110309412048</v>
       </c>
       <c r="F23" t="n">
-        <v>0.696766246778144</v>
+        <v>0.941070096967277</v>
       </c>
       <c r="G23" t="n">
-        <v>0.852263456462914</v>
+        <v>0.953593841334037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2938,21 +2644,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0000409177396454308</v>
+        <v>-0.0000153841910782729</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.35984068806455</v>
+        <v>-0.511508309696384</v>
       </c>
       <c r="F24" t="n">
-        <v>0.175447521371177</v>
+        <v>0.610118544604074</v>
       </c>
       <c r="G24" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2961,21 +2667,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0000409248632892635</v>
+        <v>-0.000028473851873237</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.39776216664206</v>
+        <v>-0.957999937576582</v>
       </c>
       <c r="F25" t="n">
-        <v>0.163769511976973</v>
+        <v>0.340364498565491</v>
       </c>
       <c r="G25" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2984,21 +2690,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0000271543530154417</v>
+        <v>-0.0000271287734149978</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.92696696247505</v>
+        <v>-0.910968826285977</v>
       </c>
       <c r="F26" t="n">
-        <v>0.355087371703465</v>
+        <v>0.364494218687098</v>
       </c>
       <c r="G26" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3007,21 +2713,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000000998035988017741</v>
+        <v>0.0000220189057214669</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0343109424118506</v>
+        <v>0.754028914995637</v>
       </c>
       <c r="F27" t="n">
-        <v>0.972664227806021</v>
+        <v>0.452597033781628</v>
       </c>
       <c r="G27" t="n">
-        <v>0.990374063080187</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3030,21 +2736,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00000902600888696443</v>
+        <v>-0.00000172745814657504</v>
       </c>
       <c r="E28" t="n">
-        <v>0.31271800982317</v>
+        <v>-0.0583399319462767</v>
       </c>
       <c r="F28" t="n">
-        <v>0.754828453683555</v>
+        <v>0.953593841334037</v>
       </c>
       <c r="G28" t="n">
-        <v>0.852263456462914</v>
+        <v>0.953593841334037</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3053,21 +2759,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0000281951249691751</v>
+        <v>0.00000865168982431432</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.946222908825322</v>
+        <v>0.3042366354589</v>
       </c>
       <c r="F29" t="n">
-        <v>0.345203701132973</v>
+        <v>0.761577415903386</v>
       </c>
       <c r="G29" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -3076,21 +2782,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0000409066551204088</v>
+        <v>0.0000630274338745638</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.39525264902946</v>
+        <v>2.10690698628527</v>
       </c>
       <c r="F30" t="n">
-        <v>0.164523613545262</v>
+        <v>0.0376182379429835</v>
       </c>
       <c r="G30" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -3099,21 +2805,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0000359332741099716</v>
+        <v>0.00000505348085102631</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.21173617726117</v>
+        <v>0.172561361601329</v>
       </c>
       <c r="F31" t="n">
-        <v>0.227076857712249</v>
+        <v>0.863343676673524</v>
       </c>
       <c r="G31" t="n">
-        <v>0.765022042104183</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -3122,21 +2828,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.000000355976367233366</v>
+        <v>-0.0000263315513244867</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0120800654556223</v>
+        <v>-0.918024888601862</v>
       </c>
       <c r="F32" t="n">
-        <v>0.990374063080187</v>
+        <v>0.360806394638331</v>
       </c>
       <c r="G32" t="n">
-        <v>0.990374063080187</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -3145,21 +2851,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0000103961573453848</v>
+        <v>0.00000997187116070892</v>
       </c>
       <c r="E33" t="n">
-        <v>0.354653331955935</v>
+        <v>0.336758409050644</v>
       </c>
       <c r="F33" t="n">
-        <v>0.723231833294816</v>
+        <v>0.73700206967425</v>
       </c>
       <c r="G33" t="n">
-        <v>0.852263456462914</v>
+        <v>0.939700796699575</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -3168,154 +2874,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0000279638886487188</v>
+        <v>-0.0000412986886677222</v>
       </c>
       <c r="E34" t="n">
-        <v>0.949740538947897</v>
+        <v>-1.40843474533081</v>
       </c>
       <c r="F34" t="n">
-        <v>0.343417452854984</v>
+        <v>0.162092210258295</v>
       </c>
       <c r="G34" t="n">
-        <v>0.765022042104183</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0000597766263171765</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.03105528387222</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0436041903410232</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.765022042104183</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0000233844497863228</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.797934972507307</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.425877008143175</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.765022042104183</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.00000484406705552648</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.168172854854611</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.866621258116848</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.913465650447488</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0000272228352448288</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.911159313239324</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.363334262557669</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.765022042104183</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.00000909583254638103</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.308770005916174</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.757825485855409</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.852263456462914</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.0000293094834482885</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-1.00688894789896</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.315233545335083</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.765022042104183</v>
+        <v>0.898063771900766</v>
       </c>
     </row>
   </sheetData>
@@ -3354,7 +2922,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -3363,21 +2931,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0268434444246806</v>
+        <v>-0.0339185670383145</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.25141387669721</v>
+        <v>-1.60843278712657</v>
       </c>
       <c r="F2" t="n">
-        <v>0.21354624513473</v>
+        <v>0.111017863119875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.438331766329183</v>
+        <v>0.309342273548139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -3386,21 +2954,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0100044663278828</v>
+        <v>0.0135500755889316</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.474417511727047</v>
+        <v>0.67937179421477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.63618092798554</v>
+        <v>0.498533880017089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.849223796250532</v>
+        <v>0.658064721622557</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -3409,21 +2977,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0192821781748053</v>
+        <v>0.00646590335328026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928135055815727</v>
+        <v>0.302381566102141</v>
       </c>
       <c r="F4" t="n">
-        <v>0.355452276352979</v>
+        <v>0.763014088748187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.602723425120268</v>
+        <v>0.833441793802656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -3432,21 +3000,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0133396481347625</v>
+        <v>0.0479199719031792</v>
       </c>
       <c r="E5" t="n">
-        <v>0.667863273116256</v>
+        <v>2.21954535207181</v>
       </c>
       <c r="F5" t="n">
-        <v>0.505676637532549</v>
+        <v>0.0287992584785148</v>
       </c>
       <c r="G5" t="n">
-        <v>0.730421809769238</v>
+        <v>0.135767932827284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -3455,21 +3023,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0359393198608317</v>
+        <v>-0.0367972242177363</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.68281150865483</v>
+        <v>-1.72250503233762</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0953634887052476</v>
+        <v>0.0881918405862394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.247945070633644</v>
+        <v>0.29103307393459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -3478,21 +3046,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00260151408043324</v>
+        <v>-0.0285509449840276</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.119713327633041</v>
+        <v>-1.33001470504471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.904937501883924</v>
+        <v>0.186658500207313</v>
       </c>
       <c r="G7" t="n">
-        <v>0.928751646670343</v>
+        <v>0.361519195321219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -3501,21 +3069,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0411856963341296</v>
+        <v>-0.0287823890158968</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.95959477450715</v>
+        <v>-1.39729378222483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0526765529287376</v>
+        <v>0.165540062518097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.171198797018397</v>
+        <v>0.361519195321219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -3524,21 +3092,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0362434871135491</v>
+        <v>-0.0339149092933548</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.74454337403795</v>
+        <v>-1.5544755090504</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0839713161834628</v>
+        <v>0.123355206518521</v>
       </c>
       <c r="G9" t="n">
-        <v>0.247945070633644</v>
+        <v>0.313132447316245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -3547,21 +3115,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0491157222169481</v>
+        <v>0.0116456576708942</v>
       </c>
       <c r="E10" t="n">
-        <v>2.28118825039049</v>
+        <v>0.512493927230992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0245423562032459</v>
+        <v>0.609480199567192</v>
       </c>
       <c r="G10" t="n">
-        <v>0.110372464123857</v>
+        <v>0.77357102252759</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -3570,21 +3138,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00891713711064758</v>
+        <v>0.00591930067768948</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.434628481071015</v>
+        <v>0.276274236882809</v>
       </c>
       <c r="F11" t="n">
-        <v>0.664718202108875</v>
+        <v>0.782930169935829</v>
       </c>
       <c r="G11" t="n">
-        <v>0.849223796250532</v>
+        <v>0.833441793802656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -3593,21 +3161,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0293895804478535</v>
+        <v>0.0180423952129375</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4352857749618</v>
+        <v>0.868032572867109</v>
       </c>
       <c r="F12" t="n">
-        <v>0.154158421853682</v>
+        <v>0.387536988758428</v>
       </c>
       <c r="G12" t="n">
-        <v>0.353657556017271</v>
+        <v>0.598638330733612</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -3616,21 +3184,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00500307011556033</v>
+        <v>-0.0261285723805493</v>
       </c>
       <c r="E13" t="n">
-        <v>0.233851463830148</v>
+        <v>-1.29858123814559</v>
       </c>
       <c r="F13" t="n">
-        <v>0.815552654908323</v>
+        <v>0.197192288357029</v>
       </c>
       <c r="G13" t="n">
-        <v>0.908758672612131</v>
+        <v>0.361519195321219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -3639,21 +3207,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0015939028083526</v>
+        <v>0.0563386489465069</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0722219985433433</v>
+        <v>2.78370202219775</v>
       </c>
       <c r="F14" t="n">
-        <v>0.942561731852972</v>
+        <v>0.00647077139836671</v>
       </c>
       <c r="G14" t="n">
-        <v>0.942561731852972</v>
+        <v>0.100623678355709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -3662,21 +3230,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0335123237594195</v>
+        <v>0.00301978792041189</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.58741659935839</v>
+        <v>0.145283959590558</v>
       </c>
       <c r="F15" t="n">
-        <v>0.115405572236777</v>
+        <v>0.884790680036838</v>
       </c>
       <c r="G15" t="n">
-        <v>0.281301082327145</v>
+        <v>0.884790680036838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -3685,21 +3253,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00860546293629614</v>
+        <v>0.00814936650664589</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.418813962933723</v>
+        <v>0.392460289848628</v>
       </c>
       <c r="F16" t="n">
-        <v>0.676201978991235</v>
+        <v>0.695586443320478</v>
       </c>
       <c r="G16" t="n">
-        <v>0.849223796250532</v>
+        <v>0.791529401019855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -3708,21 +3276,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0217028851978872</v>
+        <v>-0.0406104218478485</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.06591190112495</v>
+        <v>-1.96797977678224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.288892358595188</v>
+        <v>0.051949746053807</v>
       </c>
       <c r="G17" t="n">
-        <v>0.563340099260616</v>
+        <v>0.190482402197292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -3731,21 +3299,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0494780050161894</v>
+        <v>-0.0337737372247451</v>
       </c>
       <c r="E18" t="n">
-        <v>2.46652650901931</v>
+        <v>-1.60175862684608</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0152503297147411</v>
+        <v>0.112488099472051</v>
       </c>
       <c r="G18" t="n">
-        <v>0.110372464123857</v>
+        <v>0.309342273548139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -3754,21 +3322,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0407331287378242</v>
+        <v>-0.0137792619564022</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.97025309451609</v>
+        <v>-0.679695450923079</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0514252080631102</v>
+        <v>0.498329788605584</v>
       </c>
       <c r="G19" t="n">
-        <v>0.171198797018397</v>
+        <v>0.658064721622557</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -3777,21 +3345,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.00388801028812737</v>
+        <v>0.00851512633900681</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.184762271604792</v>
+        <v>0.416276374550504</v>
       </c>
       <c r="F20" t="n">
-        <v>0.853769566145884</v>
+        <v>0.678135140030632</v>
       </c>
       <c r="G20" t="n">
-        <v>0.924174011796105</v>
+        <v>0.791529401019855</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -3800,21 +3368,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.00841714334497445</v>
+        <v>0.0292374537678335</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.404692115030468</v>
+        <v>1.44082386387123</v>
       </c>
       <c r="F21" t="n">
-        <v>0.686521689754836</v>
+        <v>0.152881754010527</v>
       </c>
       <c r="G21" t="n">
-        <v>0.849223796250532</v>
+        <v>0.360364134453384</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -3823,21 +3391,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.028430855415026</v>
+        <v>-0.00403507402964557</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.39170076323064</v>
+        <v>-0.19128127762217</v>
       </c>
       <c r="F22" t="n">
-        <v>0.166935030009753</v>
+        <v>0.848708406704207</v>
       </c>
       <c r="G22" t="n">
-        <v>0.361692565021132</v>
+        <v>0.875230544413714</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -3846,21 +3414,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0138571870225018</v>
+        <v>-0.0212917114513815</v>
       </c>
       <c r="E23" t="n">
-        <v>0.669853107999653</v>
+        <v>-1.04242479364292</v>
       </c>
       <c r="F23" t="n">
-        <v>0.504412273300422</v>
+        <v>0.299827657731168</v>
       </c>
       <c r="G23" t="n">
-        <v>0.730421809769238</v>
+        <v>0.520753300269923</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -3869,21 +3437,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0629871851921108</v>
+        <v>-0.0537165352979813</v>
       </c>
       <c r="E24" t="n">
-        <v>2.92454809534197</v>
+        <v>-2.5546955552045</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00422159301284672</v>
+        <v>0.0121968094976617</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0461054390039062</v>
+        <v>0.100623678355709</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -3892,21 +3460,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0425162589394438</v>
+        <v>0.0634155532666746</v>
       </c>
       <c r="E25" t="n">
-        <v>2.04370000819007</v>
+        <v>3.09075448650921</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0434701366382588</v>
+        <v>0.00261146632757898</v>
       </c>
       <c r="G25" t="n">
-        <v>0.169533532889209</v>
+        <v>0.0861783888101064</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -3915,21 +3483,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.00515580556145001</v>
+        <v>-0.0538546969314414</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.244287144706642</v>
+        <v>-2.58430699120856</v>
       </c>
       <c r="F26" t="n">
-        <v>0.807482036135146</v>
+        <v>0.0112607187556153</v>
       </c>
       <c r="G26" t="n">
-        <v>0.908758672612131</v>
+        <v>0.100623678355709</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3938,21 +3506,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0349279209333887</v>
+        <v>0.0444132063989837</v>
       </c>
       <c r="E27" t="n">
-        <v>1.70986993370189</v>
+        <v>2.16250159327259</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0902241778025323</v>
+        <v>0.0330591556586651</v>
       </c>
       <c r="G27" t="n">
-        <v>0.247945070633644</v>
+        <v>0.136369017091993</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3961,21 +3529,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0167095580813253</v>
+        <v>-0.0483285378197389</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.822546637940915</v>
+        <v>-2.33159012170481</v>
       </c>
       <c r="F28" t="n">
-        <v>0.412617749253454</v>
+        <v>0.0218090532047861</v>
       </c>
       <c r="G28" t="n">
-        <v>0.643683688835388</v>
+        <v>0.119949792626323</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3984,21 +3552,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0607423709882282</v>
+        <v>-0.0166826725651727</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.88616046802902</v>
+        <v>-0.82354271350525</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00472876297475961</v>
+        <v>0.412236641687275</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0461054390039062</v>
+        <v>0.598638330733612</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4007,21 +3575,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0472643778327627</v>
+        <v>0.0291180087375336</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.27603915971355</v>
+        <v>1.32915677093562</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0248597537955321</v>
+        <v>0.18694028856193</v>
       </c>
       <c r="G30" t="n">
-        <v>0.110372464123857</v>
+        <v>0.361519195321219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4030,21 +3598,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.06680919956309</v>
+        <v>-0.0170797318816117</v>
       </c>
       <c r="E31" t="n">
-        <v>3.22471887945743</v>
+        <v>-0.814741727206533</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00167806649596977</v>
+        <v>0.417232775965851</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0461054390039062</v>
+        <v>0.598638330733612</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4053,21 +3621,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0470842263335175</v>
+        <v>0.00938405745761845</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.2662903973772</v>
+        <v>0.455452336545588</v>
       </c>
       <c r="F32" t="n">
-        <v>0.025470568643967</v>
+        <v>0.64981029283839</v>
       </c>
       <c r="G32" t="n">
-        <v>0.110372464123857</v>
+        <v>0.791529401019855</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -4076,21 +3644,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0203975158955757</v>
+        <v>0.020042451001963</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.972905841292829</v>
+        <v>0.94442799655068</v>
       </c>
       <c r="F33" t="n">
-        <v>0.332821474300967</v>
+        <v>0.347317207455008</v>
       </c>
       <c r="G33" t="n">
-        <v>0.590001704442623</v>
+        <v>0.573073392300763</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -4099,154 +3667,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00331631417822743</v>
+        <v>-0.0484664649103457</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.155427864745804</v>
+        <v>-2.3386226782598</v>
       </c>
       <c r="F34" t="n">
-        <v>0.876780472729638</v>
+        <v>0.0214251207592677</v>
       </c>
       <c r="G34" t="n">
-        <v>0.924174011796105</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0214131781835914</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.992459623477583</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.323240072031531</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.590001704442623</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0485292710864372</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.35915946936587</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0201534416345315</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.110372464123857</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.00790464079718203</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.39001623010297</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.697309413251948</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.849223796250532</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0637034179289725</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3.02242842972628</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.0031463427025076</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.0461054390039062</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0184027649459405</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.868244858326898</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.38722749820159</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.629244684577583</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.00752990181620611</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.361330099648298</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.718573981442758</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.849223796250532</v>
+        <v>0.119949792626323</v>
       </c>
     </row>
   </sheetData>
@@ -4285,7 +3715,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -4294,21 +3724,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119096898008214</v>
+        <v>0.00194336178121019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.937643744804615</v>
+        <v>1.5762286144676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.350659080686807</v>
+        <v>0.120375986619916</v>
       </c>
       <c r="G2" t="n">
-        <v>0.971431539466497</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -4317,21 +3747,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000865945738429459</v>
+        <v>0.0000569357834610953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.695533888173771</v>
+        <v>0.0501336068469638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.488314319355202</v>
+        <v>0.960187017752958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.971431539466497</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -4340,21 +3770,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00115712836683177</v>
+        <v>-0.000112593332476384</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.94175171682256</v>
+        <v>-0.0892976451055807</v>
       </c>
       <c r="F4" t="n">
-        <v>0.348561625387212</v>
+        <v>0.92915094761501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.971431539466497</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -4363,21 +3793,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000122168267559553</v>
+        <v>-0.00262752180611714</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.102900621838948</v>
+        <v>-2.05225809359047</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91824540174128</v>
+        <v>0.0446363074239478</v>
       </c>
       <c r="G5" t="n">
-        <v>0.998928309295938</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -4386,21 +3816,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00222017121544256</v>
+        <v>0.00214577527781433</v>
       </c>
       <c r="E6" t="n">
-        <v>1.76447839607992</v>
+        <v>1.70857074230973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0806675496780596</v>
+        <v>0.0928415586454965</v>
       </c>
       <c r="G6" t="n">
-        <v>0.68986013013719</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -4409,21 +3839,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000147898228993884</v>
+        <v>0.00120378622549722</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0115314728570926</v>
+        <v>0.944225602383949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.990822113781449</v>
+        <v>0.348945061936306</v>
       </c>
       <c r="G7" t="n">
-        <v>0.998928309295938</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -4432,21 +3862,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000987178769202568</v>
+        <v>0.00135141234696042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.783460156630244</v>
+        <v>1.12990363683778</v>
       </c>
       <c r="F8" t="n">
-        <v>0.435186016963051</v>
+        <v>0.263136947644552</v>
       </c>
       <c r="G8" t="n">
-        <v>0.971431539466497</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -4455,21 +3885,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00136244261905604</v>
+        <v>0.000714925790139767</v>
       </c>
       <c r="E9" t="n">
-        <v>1.10008393023234</v>
+        <v>0.542276066501165</v>
       </c>
       <c r="F9" t="n">
-        <v>0.273904551689586</v>
+        <v>0.58969197217082</v>
       </c>
       <c r="G9" t="n">
-        <v>0.971431539466497</v>
+        <v>0.884537958256229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -4478,21 +3908,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00265799096284134</v>
+        <v>-0.00117052044527671</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.08739825895568</v>
+        <v>-0.85419924534195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0393631243929756</v>
+        <v>0.396485519644235</v>
       </c>
       <c r="G10" t="n">
-        <v>0.68986013013719</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -4501,21 +3931,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000857152670783518</v>
+        <v>-0.0000482623578853353</v>
       </c>
       <c r="E11" t="n">
-        <v>0.706593586617918</v>
+        <v>-0.0381669404362641</v>
       </c>
       <c r="F11" t="n">
-        <v>0.481442201808593</v>
+        <v>0.969684769299031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.971431539466497</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -4524,21 +3954,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000517519823685524</v>
+        <v>-0.00106163898532595</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0422873335457695</v>
+        <v>-0.879995629585962</v>
       </c>
       <c r="F12" t="n">
-        <v>0.966352933086212</v>
+        <v>0.382469100388461</v>
       </c>
       <c r="G12" t="n">
-        <v>0.998928309295938</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -4547,21 +3977,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0000327005781035565</v>
+        <v>0.00138985738291495</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0258696667492305</v>
+        <v>1.20966717188763</v>
       </c>
       <c r="F13" t="n">
-        <v>0.979412219700888</v>
+        <v>0.231281336575808</v>
       </c>
       <c r="G13" t="n">
-        <v>0.998928309295938</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -4570,21 +4000,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.000548903679193624</v>
+        <v>-0.000723829968121262</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.422172072156311</v>
+        <v>-0.59041661741205</v>
       </c>
       <c r="F14" t="n">
-        <v>0.673794646986882</v>
+        <v>0.557189595849014</v>
       </c>
       <c r="G14" t="n">
-        <v>0.971431539466497</v>
+        <v>0.884537958256229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -4593,21 +4023,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000690434979338874</v>
+        <v>0.00165328097695435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.547939117923023</v>
+        <v>1.39187100501649</v>
       </c>
       <c r="F15" t="n">
-        <v>0.584939855060638</v>
+        <v>0.169240682862288</v>
       </c>
       <c r="G15" t="n">
-        <v>0.971431539466497</v>
+        <v>0.797848933493645</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -4616,21 +4046,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00187050175341397</v>
+        <v>0.000326423792387578</v>
       </c>
       <c r="E16" t="n">
-        <v>1.55433262189881</v>
+        <v>0.270657361061042</v>
       </c>
       <c r="F16" t="n">
-        <v>0.12322581984221</v>
+        <v>0.787608992667034</v>
       </c>
       <c r="G16" t="n">
-        <v>0.68986013013719</v>
+        <v>0.962633213259709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -4639,21 +4069,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000472370639253999</v>
+        <v>0.00188051850762621</v>
       </c>
       <c r="E17" t="n">
-        <v>0.389888542635552</v>
+        <v>1.55990780653568</v>
       </c>
       <c r="F17" t="n">
-        <v>0.697438028334921</v>
+        <v>0.124185580069315</v>
       </c>
       <c r="G17" t="n">
-        <v>0.971431539466497</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -4662,21 +4092,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.000608358923286195</v>
+        <v>0.000713341453974629</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.49874493887013</v>
+        <v>0.568410092538622</v>
       </c>
       <c r="F18" t="n">
-        <v>0.619041040193629</v>
+        <v>0.571936121844396</v>
       </c>
       <c r="G18" t="n">
-        <v>0.971431539466497</v>
+        <v>0.884537958256229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -4685,21 +4115,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00169457425542883</v>
+        <v>0.00193637811567041</v>
       </c>
       <c r="E19" t="n">
-        <v>1.37412844525971</v>
+        <v>1.70211506831831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.172436451301131</v>
+        <v>0.0940526744905459</v>
       </c>
       <c r="G19" t="n">
-        <v>0.840627700093015</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -4708,21 +4138,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000755835525606766</v>
+        <v>0.00115859260335725</v>
       </c>
       <c r="E20" t="n">
-        <v>0.608475867021745</v>
+        <v>0.990699108327899</v>
       </c>
       <c r="F20" t="n">
-        <v>0.544234736059449</v>
+        <v>0.325920181218996</v>
       </c>
       <c r="G20" t="n">
-        <v>0.971431539466497</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -4731,21 +4161,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0021177850961898</v>
+        <v>0.0000941011881524049</v>
       </c>
       <c r="E21" t="n">
-        <v>1.74523052264492</v>
+        <v>0.0795823763998462</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0839789990166119</v>
+        <v>0.936841528677296</v>
       </c>
       <c r="G21" t="n">
-        <v>0.68986013013719</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -4754,21 +4184,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00187190207967289</v>
+        <v>-0.00213612164142571</v>
       </c>
       <c r="E22" t="n">
-        <v>1.55184053489947</v>
+        <v>-1.77573545865549</v>
       </c>
       <c r="F22" t="n">
-        <v>0.123821048998983</v>
+        <v>0.0809873361236008</v>
       </c>
       <c r="G22" t="n">
-        <v>0.68986013013719</v>
+        <v>0.68302069038123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -4777,21 +4207,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000286731801107968</v>
+        <v>0.000559820822375301</v>
       </c>
       <c r="E23" t="n">
-        <v>0.233763954865486</v>
+        <v>0.473241039476675</v>
       </c>
       <c r="F23" t="n">
-        <v>0.815640290916721</v>
+        <v>0.637805637927916</v>
       </c>
       <c r="G23" t="n">
-        <v>0.998928309295938</v>
+        <v>0.91511243702701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -4800,21 +4230,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.00207452486832814</v>
+        <v>0.00101262856796017</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.59205836807405</v>
+        <v>0.788992281367948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.114489363956167</v>
+        <v>0.43330841414825</v>
       </c>
       <c r="G24" t="n">
-        <v>0.68986013013719</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -4823,21 +4253,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.00105611989813678</v>
+        <v>0.000438585646602918</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.845472585345584</v>
+        <v>0.345310721940638</v>
       </c>
       <c r="F25" t="n">
-        <v>0.399840872875202</v>
+        <v>0.731101653230989</v>
       </c>
       <c r="G25" t="n">
-        <v>0.971431539466497</v>
+        <v>0.949568395726011</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -4846,21 +4276,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.00210279397566728</v>
+        <v>0.000462704829252676</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.70900481598514</v>
+        <v>0.363391580517327</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0905140358221196</v>
+        <v>0.717624710171412</v>
       </c>
       <c r="G26" t="n">
-        <v>0.68986013013719</v>
+        <v>0.949568395726011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -4869,21 +4299,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0000558665812720343</v>
+        <v>-0.00100234676368229</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0455817918837061</v>
+        <v>-0.820263944346719</v>
       </c>
       <c r="F27" t="n">
-        <v>0.963733374316398</v>
+        <v>0.415401598830523</v>
       </c>
       <c r="G27" t="n">
-        <v>0.998928309295938</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -4892,21 +4322,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000121974898856765</v>
+        <v>0.000889246567271738</v>
       </c>
       <c r="E28" t="n">
-        <v>0.10102462970228</v>
+        <v>0.712648061074379</v>
       </c>
       <c r="F28" t="n">
-        <v>0.919730717644762</v>
+        <v>0.47890173452728</v>
       </c>
       <c r="G28" t="n">
-        <v>0.998928309295938</v>
+        <v>0.831776696810538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -4915,21 +4345,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>0.000870064810580566</v>
+        <v>0.000148692678182045</v>
       </c>
       <c r="E29" t="n">
-        <v>0.676184829259913</v>
+        <v>0.127524149047456</v>
       </c>
       <c r="F29" t="n">
-        <v>0.500465182636663</v>
+        <v>0.898963720013168</v>
       </c>
       <c r="G29" t="n">
-        <v>0.971431539466497</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4938,21 +4368,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.000528086388253226</v>
+        <v>0.000113862355046088</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.42055532888631</v>
+        <v>0.086055801032313</v>
       </c>
       <c r="F30" t="n">
-        <v>0.674971190470647</v>
+        <v>0.931716465015435</v>
       </c>
       <c r="G30" t="n">
-        <v>0.971431539466497</v>
+        <v>0.969684769299031</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4961,21 +4391,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.000501948575737426</v>
+        <v>0.000945089436151371</v>
       </c>
       <c r="E31" t="n">
-        <v>0.391993124781762</v>
+        <v>0.772667166715801</v>
       </c>
       <c r="F31" t="n">
-        <v>0.695887273183409</v>
+        <v>0.442835772056308</v>
       </c>
       <c r="G31" t="n">
-        <v>0.971431539466497</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4984,21 +4414,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.000862994110301583</v>
+        <v>0.00129309257509762</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6880949670834</v>
+        <v>1.09505656663639</v>
       </c>
       <c r="F32" t="n">
-        <v>0.492966638959999</v>
+        <v>0.277988200239125</v>
       </c>
       <c r="G32" t="n">
-        <v>0.971431539466497</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -5007,21 +4437,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.000233643164053436</v>
+        <v>-0.00106231242947138</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.187676324612265</v>
+        <v>-0.852047702439141</v>
       </c>
       <c r="F33" t="n">
-        <v>0.851506037092677</v>
+        <v>0.397668761992267</v>
       </c>
       <c r="G33" t="n">
-        <v>0.998928309295938</v>
+        <v>0.811865582103231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -5030,154 +4460,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.000656637471873989</v>
+        <v>-0.000403938501579606</v>
       </c>
       <c r="E34" t="n">
-        <v>0.521556602478225</v>
+        <v>-0.322607541608739</v>
       </c>
       <c r="F34" t="n">
-        <v>0.603118248118887</v>
+        <v>0.748144796632615</v>
       </c>
       <c r="G34" t="n">
-        <v>0.971431539466497</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.000278219972597262</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.217508657840237</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.828249742649686</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.998928309295938</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-0.000850308101323678</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.683070797373839</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.496122353000217</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.971431539466497</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.00033040275801234</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.274968732143536</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.783900645191056</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.998928309295938</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0000017446463674822</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.00134648645172227</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.998928309295938</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.998928309295938</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.00108688752272655</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.867953769494078</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.387472459223745</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.971431539466497</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.00142880004107174</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.1659325709184</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.246381215900369</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.971431539466497</v>
+        <v>0.949568395726011</v>
       </c>
     </row>
   </sheetData>
@@ -5216,7 +4508,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -5225,21 +4517,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00608185043717783</v>
+        <v>0.00184920850216181</v>
       </c>
       <c r="E2" t="n">
-        <v>0.84578755332739</v>
+        <v>0.261503790585141</v>
       </c>
       <c r="F2" t="n">
-        <v>0.398458735168039</v>
+        <v>0.793852337104153</v>
       </c>
       <c r="G2" t="n">
-        <v>0.871055851107529</v>
+        <v>0.903349211187485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -5248,21 +4540,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00391547523045507</v>
+        <v>0.00355591970475622</v>
       </c>
       <c r="E3" t="n">
-        <v>0.555362519476846</v>
+        <v>0.502856481961374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.579130229317797</v>
+        <v>0.615370128025247</v>
       </c>
       <c r="G3" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -5271,21 +4563,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000491477435297657</v>
+        <v>0.00746811539310702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00691042095600728</v>
+        <v>1.05609534108331</v>
       </c>
       <c r="F4" t="n">
-        <v>0.994491691419944</v>
+        <v>0.29162700989523</v>
       </c>
       <c r="G4" t="n">
-        <v>0.994491691419944</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -5294,21 +4586,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00244106461877475</v>
+        <v>0.00456001100612502</v>
       </c>
       <c r="E5" t="n">
-        <v>0.348462901797178</v>
+        <v>0.644848951222978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.72777810039017</v>
+        <v>0.519432392500189</v>
       </c>
       <c r="G5" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -5317,21 +4609,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0120880459705656</v>
+        <v>-0.0119092522133839</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6922204404652</v>
+        <v>-1.68413382979454</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0918169762662114</v>
+        <v>0.0930154148542891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.682889645136113</v>
+        <v>0.767377172547885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -5340,21 +4632,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0141518618556105</v>
+        <v>0.00615841551124155</v>
       </c>
       <c r="E7" t="n">
-        <v>1.97508509612508</v>
+        <v>0.870885569856135</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0493295295962843</v>
+        <v>0.384392207837544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.513634383990872</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -5363,21 +4655,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00774566029807401</v>
+        <v>-0.000471758598212097</v>
       </c>
       <c r="E8" t="n">
-        <v>1.08809848651398</v>
+        <v>-0.0667132243494311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.277571869086045</v>
+        <v>0.946846734235333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.871055851107529</v>
+        <v>0.946846734235333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -5386,21 +4678,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00108019120003823</v>
+        <v>0.00994709402565394</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1513413417772</v>
+        <v>1.40665738340182</v>
       </c>
       <c r="F9" t="n">
-        <v>0.879825289667696</v>
+        <v>0.160384536922186</v>
       </c>
       <c r="G9" t="n">
-        <v>0.967997027073274</v>
+        <v>0.820672465323933</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -5409,21 +4701,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00488078949092512</v>
+        <v>0.0194799837135037</v>
       </c>
       <c r="E10" t="n">
-        <v>0.677957092701318</v>
+        <v>2.75474051501646</v>
       </c>
       <c r="F10" t="n">
-        <v>0.498409347960426</v>
+        <v>0.0061697512555127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.871055851107529</v>
+        <v>0.203601791431919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -5432,21 +4724,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00436139935633551</v>
+        <v>-0.0136364437729763</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.617238817810693</v>
+        <v>-1.92838272837576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.537624160570111</v>
+        <v>0.0545871227117113</v>
       </c>
       <c r="G11" t="n">
-        <v>0.87363926092643</v>
+        <v>0.600458349828825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -5455,21 +4747,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00498017382814984</v>
+        <v>-0.00295065350764351</v>
       </c>
       <c r="E12" t="n">
-        <v>0.708848878755064</v>
+        <v>-0.417263427055455</v>
       </c>
       <c r="F12" t="n">
-        <v>0.479061321089706</v>
+        <v>0.676732403769751</v>
       </c>
       <c r="G12" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
@@ -5478,21 +4770,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0137570435684373</v>
+        <v>-0.00596973210694803</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.94654018034711</v>
+        <v>-0.84420311334267</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0526804496400894</v>
+        <v>0.399111917752937</v>
       </c>
       <c r="G13" t="n">
-        <v>0.513634383990872</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
@@ -5501,21 +4793,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0163251904579188</v>
+        <v>0.00912110635857945</v>
       </c>
       <c r="E14" t="n">
-        <v>2.28863234103257</v>
+        <v>1.28985124409192</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0229133569900846</v>
+        <v>0.197923444779492</v>
       </c>
       <c r="G14" t="n">
-        <v>0.513634383990872</v>
+        <v>0.820672465323933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B15" t="n">
         <v>13</v>
@@ -5524,21 +4816,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00291839771836077</v>
+        <v>-0.00385556185678904</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.40794484984769</v>
+        <v>-0.545230047994662</v>
       </c>
       <c r="F15" t="n">
-        <v>0.683654103892192</v>
+        <v>0.585930149454449</v>
       </c>
       <c r="G15" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -5547,21 +4839,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0049824353219826</v>
+        <v>0.00230699180290131</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.704898197496591</v>
+        <v>0.326240713582202</v>
       </c>
       <c r="F16" t="n">
-        <v>0.481512473761562</v>
+        <v>0.744430241793397</v>
       </c>
       <c r="G16" t="n">
-        <v>0.871055851107529</v>
+        <v>0.877364213542217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>13</v>
@@ -5570,21 +4862,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.00675514950931708</v>
+        <v>-0.00567267539717313</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.958078772575091</v>
+        <v>-0.802195164788423</v>
       </c>
       <c r="F17" t="n">
-        <v>0.33892424266399</v>
+        <v>0.422964925257543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
         <v>13</v>
@@ -5593,21 +4885,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00818486617938133</v>
+        <v>-0.00301285995867176</v>
       </c>
       <c r="E18" t="n">
-        <v>1.15874977885039</v>
+        <v>-0.426060284047903</v>
       </c>
       <c r="F18" t="n">
-        <v>0.247634696310564</v>
+        <v>0.670316439186033</v>
       </c>
       <c r="G18" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B19" t="n">
         <v>13</v>
@@ -5616,21 +4908,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.00608630038031796</v>
+        <v>0.00115034517538856</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.85680831134835</v>
+        <v>0.162674800323363</v>
       </c>
       <c r="F19" t="n">
-        <v>0.392349745644428</v>
+        <v>0.870865007687541</v>
       </c>
       <c r="G19" t="n">
-        <v>0.871055851107529</v>
+        <v>0.93219551010374</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>13</v>
@@ -5639,21 +4931,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0115094155417167</v>
+        <v>0.005185904012294</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.62654671554529</v>
+        <v>0.73335892369097</v>
       </c>
       <c r="F20" t="n">
-        <v>0.105059945405556</v>
+        <v>0.463812885942424</v>
       </c>
       <c r="G20" t="n">
-        <v>0.682889645136113</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B21" t="n">
         <v>13</v>
@@ -5662,21 +4954,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00320903132021825</v>
+        <v>0.00499573354845563</v>
       </c>
       <c r="E21" t="n">
-        <v>0.451730902968894</v>
+        <v>0.706466176284211</v>
       </c>
       <c r="F21" t="n">
-        <v>0.651844174263789</v>
+        <v>0.480351477962179</v>
       </c>
       <c r="G21" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
         <v>13</v>
@@ -5685,21 +4977,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.000306397530633714</v>
+        <v>0.00321605820361375</v>
       </c>
       <c r="E22" t="n">
-        <v>0.043283348013538</v>
+        <v>0.454795340819737</v>
       </c>
       <c r="F22" t="n">
-        <v>0.965509303924675</v>
+        <v>0.649528342837805</v>
       </c>
       <c r="G22" t="n">
-        <v>0.994491691419944</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>13</v>
@@ -5708,21 +5000,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00352791679015995</v>
+        <v>-0.00910020170495043</v>
       </c>
       <c r="E23" t="n">
-        <v>0.49845828496326</v>
+        <v>-1.28689503544456</v>
       </c>
       <c r="F23" t="n">
-        <v>0.618587756933537</v>
+        <v>0.19895090068459</v>
       </c>
       <c r="G23" t="n">
-        <v>0.876372174499355</v>
+        <v>0.820672465323933</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B24" t="n">
         <v>13</v>
@@ -5731,21 +5023,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00696724903187765</v>
+        <v>-0.00349262758228478</v>
       </c>
       <c r="E24" t="n">
-        <v>0.954794379691152</v>
+        <v>-0.493906095933453</v>
       </c>
       <c r="F24" t="n">
-        <v>0.340579681375461</v>
+        <v>0.621671217834692</v>
       </c>
       <c r="G24" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" t="n">
         <v>13</v>
@@ -5754,21 +5046,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00768130009664346</v>
+        <v>0.00275552122977266</v>
       </c>
       <c r="E25" t="n">
-        <v>1.07789019892362</v>
+        <v>0.389669010163533</v>
       </c>
       <c r="F25" t="n">
-        <v>0.282094319485467</v>
+        <v>0.697009832941204</v>
       </c>
       <c r="G25" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
         <v>13</v>
@@ -5777,21 +5069,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00294357914799749</v>
+        <v>-0.00745932841007167</v>
       </c>
       <c r="E26" t="n">
-        <v>0.412380463411741</v>
+        <v>-1.05485273952223</v>
       </c>
       <c r="F26" t="n">
-        <v>0.680404660664156</v>
+        <v>0.292194254478219</v>
       </c>
       <c r="G26" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B27" t="n">
         <v>13</v>
@@ -5800,21 +5092,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00588116557838678</v>
+        <v>0.00493375806251794</v>
       </c>
       <c r="E27" t="n">
-        <v>0.830347324068865</v>
+        <v>0.697701980966531</v>
       </c>
       <c r="F27" t="n">
-        <v>0.40711379110011</v>
+        <v>0.485810232730226</v>
       </c>
       <c r="G27" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
         <v>13</v>
@@ -5823,21 +5115,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00512876400596511</v>
+        <v>-0.00415674713249599</v>
       </c>
       <c r="E28" t="n">
-        <v>0.728614598483853</v>
+        <v>-0.587821833168548</v>
       </c>
       <c r="F28" t="n">
-        <v>0.466901425723493</v>
+        <v>0.557017381562807</v>
       </c>
       <c r="G28" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B29" t="n">
         <v>13</v>
@@ -5846,21 +5138,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.00717758199628263</v>
+        <v>0.005121753377285</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.993945199109376</v>
+        <v>0.72428713205488</v>
       </c>
       <c r="F29" t="n">
-        <v>0.321185258825035</v>
+        <v>0.469356017653993</v>
       </c>
       <c r="G29" t="n">
-        <v>0.871055851107529</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B30" t="n">
         <v>13</v>
@@ -5869,21 +5161,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00912018484868782</v>
+        <v>0.0157656105750702</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.27699312042986</v>
+        <v>2.22947651465497</v>
       </c>
       <c r="F30" t="n">
-        <v>0.202758219620455</v>
+        <v>0.0263934874636092</v>
       </c>
       <c r="G30" t="n">
-        <v>0.871055851107529</v>
+        <v>0.435492543149552</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B31" t="n">
         <v>13</v>
@@ -5892,21 +5184,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00237420358268127</v>
+        <v>0.00473860448139248</v>
       </c>
       <c r="E31" t="n">
-        <v>0.330163428963091</v>
+        <v>0.67010455149824</v>
       </c>
       <c r="F31" t="n">
-        <v>0.741545686114839</v>
+        <v>0.503217201459124</v>
       </c>
       <c r="G31" t="n">
-        <v>0.876372174499355</v>
+        <v>0.851900906928139</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B32" t="n">
         <v>13</v>
@@ -5915,21 +5207,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00330619821027655</v>
+        <v>-0.00104629307150124</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.462544587600032</v>
+        <v>-0.147960386262924</v>
       </c>
       <c r="F32" t="n">
-        <v>0.644082547936519</v>
+        <v>0.882456183183427</v>
       </c>
       <c r="G32" t="n">
-        <v>0.876372174499355</v>
+        <v>0.93219551010374</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B33" t="n">
         <v>13</v>
@@ -5938,21 +5230,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00269312558697095</v>
+        <v>-0.000853954179753151</v>
       </c>
       <c r="E33" t="n">
-        <v>0.379004765139638</v>
+        <v>-0.120760993003446</v>
       </c>
       <c r="F33" t="n">
-        <v>0.704997532263968</v>
+        <v>0.903947161312718</v>
       </c>
       <c r="G33" t="n">
-        <v>0.876372174499355</v>
+        <v>0.93219551010374</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B34" t="n">
         <v>13</v>
@@ -5961,154 +5253,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0093318176051528</v>
+        <v>-0.0102015218199118</v>
       </c>
       <c r="E34" t="n">
-        <v>1.30537568280167</v>
+        <v>-1.44263701065903</v>
       </c>
       <c r="F34" t="n">
-        <v>0.192933391991317</v>
+        <v>0.149985041206138</v>
       </c>
       <c r="G34" t="n">
-        <v>0.871055851107529</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="n">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.015114662943701</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.11260658057288</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0355999071028699</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.513634383990872</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="n">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.00466581963444789</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.653996080996674</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.513699604499312</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.871055851107529</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.000265781854396581</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.0378542649883049</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.969833291118722</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.994491691419944</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" t="n">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.00609316008220476</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.841005629379797</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.401127264106154</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.871055851107529</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="n">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.000958784449792053</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.133964330300968</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.893535717298406</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.967997027073274</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="n">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.00125072916894021</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.176006169465728</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.860427822104749</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.967997027073274</v>
+        <v>0.820672465323933</v>
       </c>
     </row>
   </sheetData>
@@ -6147,7 +5301,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -6156,21 +5310,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0131486986203692</v>
+        <v>-0.115583228329762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.163568778850274</v>
+        <v>-1.44408384712419</v>
       </c>
       <c r="F2" t="n">
-        <v>0.870141235614412</v>
+        <v>0.149506077817501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.882979434387135</v>
+        <v>0.704814366853934</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -6179,21 +5333,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.102806691901572</v>
+        <v>0.0328591527641644</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.27890717838236</v>
+        <v>0.410538556697309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.20156352701306</v>
+        <v>0.681632963491008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -6202,21 +5356,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.045297094995611</v>
+        <v>-0.0608916471177993</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.563492306563254</v>
+        <v>-0.760773386401063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.573369582235673</v>
+        <v>0.447245183802429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -6225,21 +5379,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0359129371715789</v>
+        <v>0.0865583585308439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.446754119756135</v>
+        <v>1.08145039028807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.65525926189031</v>
+        <v>0.28015494407975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -6248,21 +5402,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.106177349342493</v>
+        <v>-0.116805428441899</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.32083789239841</v>
+        <v>-1.45935387777998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.187200906757514</v>
+        <v>0.145260505777073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.882979434387135</v>
+        <v>0.704814366853934</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -6271,21 +5425,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0509162438411223</v>
+        <v>0.00748583243608725</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6333940771776</v>
+        <v>0.0935271480079294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.526785734172314</v>
+        <v>0.925532083878519</v>
       </c>
       <c r="G7" t="n">
-        <v>0.882979434387135</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -6294,21 +5448,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0632437817691562</v>
+        <v>-0.005708758233047</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.786747681464737</v>
+        <v>-0.0713245829054046</v>
       </c>
       <c r="F8" t="n">
-        <v>0.431827792043507</v>
+        <v>0.943175437575312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.882979434387135</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -6317,21 +5471,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0266639805586513</v>
+        <v>-0.048431848888109</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.33169782540377</v>
+        <v>-0.605102069533292</v>
       </c>
       <c r="F9" t="n">
-        <v>0.740265930736088</v>
+        <v>0.54545776834545</v>
       </c>
       <c r="G9" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -6340,21 +5494,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0856255713241766</v>
+        <v>-0.036017636903238</v>
       </c>
       <c r="E10" t="n">
-        <v>1.06517538687485</v>
+        <v>-0.450000302078059</v>
       </c>
       <c r="F10" t="n">
-        <v>0.287345801150929</v>
+        <v>0.652956456557959</v>
       </c>
       <c r="G10" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -6363,21 +5517,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0242662788513823</v>
+        <v>0.0651071156204348</v>
       </c>
       <c r="E11" t="n">
-        <v>0.301870604351062</v>
+        <v>0.81344097546813</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7628848018192</v>
+        <v>0.416454087176346</v>
       </c>
       <c r="G11" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -6386,21 +5540,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0566354392027176</v>
+        <v>-0.036229350145168</v>
       </c>
       <c r="E12" t="n">
-        <v>0.704540418599791</v>
+        <v>-0.452645423496723</v>
       </c>
       <c r="F12" t="n">
-        <v>0.481446731264974</v>
+        <v>0.65105196138555</v>
       </c>
       <c r="G12" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -6409,21 +5563,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.060997025911127</v>
+        <v>-0.00379386090767513</v>
       </c>
       <c r="E13" t="n">
-        <v>0.758798214929454</v>
+        <v>-0.0474000712229532</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4483552525726</v>
+        <v>0.962218267581504</v>
       </c>
       <c r="G13" t="n">
-        <v>0.882979434387135</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -6432,21 +5586,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0329968935176852</v>
+        <v>0.0227670630394146</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.410478765569936</v>
+        <v>0.284449123430575</v>
       </c>
       <c r="F14" t="n">
-        <v>0.68164263515137</v>
+        <v>0.776214901713688</v>
       </c>
       <c r="G14" t="n">
-        <v>0.882979434387135</v>
+        <v>0.948707102094507</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -6455,21 +5609,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0299260714028422</v>
+        <v>0.0772417542912577</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.372277979477451</v>
+        <v>0.965049785400564</v>
       </c>
       <c r="F15" t="n">
-        <v>0.70985440946357</v>
+        <v>0.33510883867516</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -6478,21 +5632,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.033880879501414</v>
+        <v>-0.0349799878033043</v>
       </c>
       <c r="E16" t="n">
-        <v>0.421475481827109</v>
+        <v>-0.437036030999542</v>
       </c>
       <c r="F16" t="n">
-        <v>0.673601424346121</v>
+        <v>0.662323437442651</v>
       </c>
       <c r="G16" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -6501,21 +5655,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0194927436151177</v>
+        <v>-0.0385468956414613</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.242488200667021</v>
+        <v>-0.48160057611302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.808508129066933</v>
+        <v>0.630355745819395</v>
       </c>
       <c r="G17" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -6524,21 +5678,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0213091376876988</v>
+        <v>-0.0336408044918192</v>
       </c>
       <c r="E18" t="n">
-        <v>0.265084000368651</v>
+        <v>-0.420304425416279</v>
       </c>
       <c r="F18" t="n">
-        <v>0.791061468182138</v>
+        <v>0.674491048072555</v>
       </c>
       <c r="G18" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -6547,21 +5701,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0345903902505456</v>
+        <v>0.00847435843083433</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.430301739859734</v>
+        <v>0.105877680538513</v>
       </c>
       <c r="F19" t="n">
-        <v>0.66717424213402</v>
+        <v>0.915733014352728</v>
       </c>
       <c r="G19" t="n">
-        <v>0.882979434387135</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -6570,21 +5724,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0870892240873742</v>
+        <v>0.0638430332139512</v>
       </c>
       <c r="E20" t="n">
-        <v>1.08338311237296</v>
+        <v>0.797647672140168</v>
       </c>
       <c r="F20" t="n">
-        <v>0.279196244539563</v>
+        <v>0.425553007798114</v>
       </c>
       <c r="G20" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -6593,21 +5747,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0525152748553331</v>
+        <v>0.0570014147380473</v>
       </c>
       <c r="E21" t="n">
-        <v>0.653285897493033</v>
+        <v>0.712169260851537</v>
       </c>
       <c r="F21" t="n">
-        <v>0.513892796128405</v>
+        <v>0.476779332213227</v>
       </c>
       <c r="G21" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -6616,21 +5770,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0243350178616169</v>
+        <v>-0.0547081163064735</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.302725712243339</v>
+        <v>-0.683517048333104</v>
       </c>
       <c r="F22" t="n">
-        <v>0.762233406418714</v>
+        <v>0.494679911863585</v>
       </c>
       <c r="G22" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -6639,21 +5793,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0276123116800861</v>
+        <v>-0.0348771224631589</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.343494990123822</v>
+        <v>-0.435750843016134</v>
       </c>
       <c r="F23" t="n">
-        <v>0.73138036563074</v>
+        <v>0.66325494139519</v>
       </c>
       <c r="G23" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -6662,21 +5816,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0540892762131389</v>
+        <v>-0.137567169116884</v>
       </c>
       <c r="E24" t="n">
-        <v>0.672866350847263</v>
+        <v>-1.71874872926647</v>
       </c>
       <c r="F24" t="n">
-        <v>0.501364421518453</v>
+        <v>0.0864416752008804</v>
       </c>
       <c r="G24" t="n">
-        <v>0.882979434387135</v>
+        <v>0.63653006042801</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -6685,21 +5839,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0305203388313067</v>
+        <v>0.0362901536492382</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.37967061964595</v>
+        <v>0.453405095633808</v>
       </c>
       <c r="F25" t="n">
-        <v>0.704362155265818</v>
+        <v>0.65050541683051</v>
       </c>
       <c r="G25" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -6708,21 +5862,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0560154019276139</v>
+        <v>-0.154443288614163</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.69682720356167</v>
+        <v>-1.92959706704285</v>
       </c>
       <c r="F26" t="n">
-        <v>0.486256907947713</v>
+        <v>0.0543708403133076</v>
       </c>
       <c r="G26" t="n">
-        <v>0.882979434387135</v>
+        <v>0.598079243446384</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -6731,21 +5885,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0651340152321398</v>
+        <v>0.13336940411967</v>
       </c>
       <c r="E27" t="n">
-        <v>0.810262037387626</v>
+        <v>1.6663023258038</v>
       </c>
       <c r="F27" t="n">
-        <v>0.418201399646194</v>
+        <v>0.0964439485496985</v>
       </c>
       <c r="G27" t="n">
-        <v>0.882979434387135</v>
+        <v>0.63653006042801</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -6754,21 +5908,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.011838794480011</v>
+        <v>-0.0998167831557719</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.14727367415319</v>
+        <v>-1.24709965546128</v>
       </c>
       <c r="F28" t="n">
-        <v>0.882979434387135</v>
+        <v>0.213098026277179</v>
       </c>
       <c r="G28" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -6777,21 +5931,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.176827377550801</v>
+        <v>-0.0131019434438131</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.19971869828046</v>
+        <v>-0.163694206906603</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0283150354933123</v>
+        <v>0.870055389215496</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338012943026985</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -6800,21 +5954,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.174001162909228</v>
+        <v>0.198767660908858</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.16456080995723</v>
+        <v>2.48338078626958</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0309262537481122</v>
+        <v>0.0134271811602324</v>
       </c>
       <c r="G30" t="n">
-        <v>0.338012943026985</v>
+        <v>0.425913983423454</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -6823,21 +5977,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0146976063322618</v>
+        <v>-0.0169533334840849</v>
       </c>
       <c r="E31" t="n">
-        <v>0.182837069218839</v>
+        <v>-0.211813040637945</v>
       </c>
       <c r="F31" t="n">
-        <v>0.855005039186608</v>
+        <v>0.832361865997048</v>
       </c>
       <c r="G31" t="n">
-        <v>0.882979434387135</v>
+        <v>0.962218267581504</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -6846,21 +6000,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0943385140733982</v>
+        <v>-0.0600064243869973</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.17356371083223</v>
+        <v>-0.749713513224557</v>
       </c>
       <c r="F32" t="n">
-        <v>0.241166721945793</v>
+        <v>0.453872420173975</v>
       </c>
       <c r="G32" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -6869,21 +6023,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0124795150564339</v>
+        <v>0.0643308977836373</v>
       </c>
       <c r="E33" t="n">
-        <v>0.155244187836376</v>
+        <v>0.803742997170007</v>
       </c>
       <c r="F33" t="n">
-        <v>0.876695746724885</v>
+        <v>0.422027611909412</v>
       </c>
       <c r="G33" t="n">
-        <v>0.882979434387135</v>
+        <v>0.86514953058474</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -6892,154 +6046,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0613044207613912</v>
+        <v>-0.179083056799907</v>
       </c>
       <c r="E34" t="n">
-        <v>0.762622182740587</v>
+        <v>-2.23744355781919</v>
       </c>
       <c r="F34" t="n">
-        <v>0.446072952702666</v>
+        <v>0.0258129686923305</v>
       </c>
       <c r="G34" t="n">
-        <v>0.882979434387135</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.170290060657679</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.11839498921707</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0346679941566138</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.338012943026985</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.142760512453753</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.77592957024092</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0763942132883246</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.595874863648932</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0145274021308315</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.180719742311673</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.856665794100384</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.882979434387135</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.185514421162512</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.30778483899993</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.021446435404784</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.338012943026985</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0594109578493317</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.739067652724661</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.460236424490422</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.882979434387135</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.067899241813032</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.844661239022696</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.398731585867601</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.882979434387135</v>
+        <v>0.425913983423454</v>
       </c>
     </row>
   </sheetData>
@@ -7055,97 +6071,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00247246904545623</v>
+        <v>0.00225963595743908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0049824353219826</v>
+        <v>0.00493375806251794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -7154,24 +6170,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000850308101323678</v>
+        <v>0.00100234676368229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -7180,24 +6196,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000215579778367726</v>
+        <v>0.0000169781436644301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -7206,59 +6222,59 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000233844497863228</v>
+        <v>0.0000214245831758299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0217028851978872</v>
+        <v>0.0285509449840276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0525152748553331</v>
+        <v>0.0547081163064735</v>
       </c>
     </row>
   </sheetData>
